--- a/util/tests-results.xlsx
+++ b/util/tests-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erans\Projects\IoT\util\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77CF1D9D-5EAD-4493-80CD-2AD90CF8C0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C21D1C9-DD0B-4CE8-BBBD-3147C894AB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AAB7D5D3-A07A-4FFB-8640-982B985A9BC0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="18">
   <si>
     <t>label</t>
   </si>
@@ -59,37 +59,37 @@
     <t>total</t>
   </si>
   <si>
-    <t>precision</t>
-  </si>
-  <si>
     <t>lehit test - outside audio</t>
   </si>
   <si>
     <t>unknown test - outside audio</t>
   </si>
   <si>
-    <t>recoil lehit</t>
-  </si>
-  <si>
-    <t>recoil shalom:</t>
-  </si>
-  <si>
     <t>shalom test - mic audio</t>
   </si>
   <si>
-    <t>lehit recoil:</t>
-  </si>
-  <si>
-    <t>shalom recoil:</t>
-  </si>
-  <si>
-    <t>lehit recoil</t>
-  </si>
-  <si>
     <t>lehit test - mic audio</t>
   </si>
   <si>
-    <t>shalom recoil</t>
+    <t>false lehit:</t>
+  </si>
+  <si>
+    <t>false shalom :</t>
+  </si>
+  <si>
+    <t>false shalom:</t>
+  </si>
+  <si>
+    <t>false lehit</t>
+  </si>
+  <si>
+    <t>false shalom</t>
+  </si>
+  <si>
+    <t>model precision:</t>
+  </si>
+  <si>
+    <t>recoil</t>
   </si>
 </sst>
 </file>
@@ -461,20 +461,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F067EE-1261-4016-B1FB-FAE397679600}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1">
+        <f>(B3+B11+B19)/(B6+B13+B20) * 100</f>
+        <v>47.169811320754718</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -482,7 +490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -490,14 +498,14 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E3">
         <f>B3/B6 * 100</f>
         <v>38.983050847457626</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -505,14 +513,14 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <f>B4/B6*100</f>
         <v>15.254237288135593</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -520,7 +528,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -529,12 +537,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -542,7 +550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -550,14 +558,14 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <f>B11/B13*100</f>
         <v>57.999999999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -565,14 +573,14 @@
         <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11">
         <f>B10/B13*100</f>
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -580,7 +588,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -589,12 +597,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -602,7 +610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -610,14 +618,14 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E17">
         <f>B17/B20*100</f>
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -625,14 +633,14 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <f>B18/B20*100</f>
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -640,7 +648,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -649,12 +657,19 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="I22" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22">
+        <f>(B24+B32+B40)/(B27+B34+B41) * 100</f>
+        <v>57.333333333333336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -662,7 +677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -670,14 +685,14 @@
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <f>B24/B27 * 100</f>
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -685,14 +700,14 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <f>B25/B27*100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -700,7 +715,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -709,12 +724,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -722,7 +737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -730,14 +745,14 @@
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E31">
         <f>B32/B34 * 100</f>
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -745,7 +760,7 @@
         <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E32">
         <f>B31/B34*100</f>
@@ -771,7 +786,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -790,7 +805,7 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E38">
         <f>B38/B41*100</f>
@@ -805,7 +820,7 @@
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E39">
         <f>B39/B41*100</f>
